--- a/templates/prevpay_detailed_template.xlsx
+++ b/templates/prevpay_detailed_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438D4271-D973-4465-84F9-3698645BDE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CAEA05-B50F-485C-B743-6678A8586739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="1950" windowWidth="28170" windowHeight="11295" xr2:uid="{ED791CAF-94D7-43DB-AB40-3A7CD8C47D66}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{ED791CAF-94D7-43DB-AB40-3A7CD8C47D66}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -1053,9 +1053,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1093,7 +1093,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1199,7 +1199,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1341,7 +1341,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1349,7 +1349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5909BD8-EFCE-446A-B529-563847BE478D}">
-  <dimension ref="A1:O1481"/>
+  <dimension ref="A1:O1503"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
@@ -2135,395 +2135,393 @@
     </row>
     <row r="44" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="37"/>
-      <c r="K44" s="35"/>
-      <c r="L44" s="37"/>
-      <c r="M44" s="38"/>
-      <c r="N44" s="39"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="23"/>
+      <c r="L44" s="25"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="27"/>
       <c r="O44" s="1"/>
     </row>
     <row r="45" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="40"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="3"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="25"/>
+      <c r="K45" s="23"/>
+      <c r="L45" s="25"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="27"/>
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="1:15" ht="19.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
-      <c r="B46" s="40"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="N46" s="43"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="23"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="23"/>
+      <c r="L46" s="25"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="27"/>
       <c r="O46" s="1"/>
     </row>
     <row r="47" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
-      <c r="B47" s="40"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-      <c r="N47" s="3"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="23"/>
+      <c r="J47" s="25"/>
+      <c r="K47" s="23"/>
+      <c r="L47" s="25"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="27"/>
       <c r="O47" s="1"/>
     </row>
     <row r="48" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
-      <c r="B48" s="40"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="3"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="23"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="23"/>
+      <c r="L48" s="25"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="27"/>
       <c r="O48" s="1"/>
     </row>
     <row r="49" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A49" s="1"/>
-      <c r="B49" s="40"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="3"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="25"/>
+      <c r="K49" s="23"/>
+      <c r="L49" s="25"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="27"/>
       <c r="O49" s="1"/>
     </row>
     <row r="50" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A50" s="1"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="3"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="23"/>
+      <c r="J50" s="25"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="27"/>
       <c r="O50" s="1"/>
     </row>
     <row r="51" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="3"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="23"/>
+      <c r="J51" s="25"/>
+      <c r="K51" s="23"/>
+      <c r="L51" s="25"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="27"/>
       <c r="O51" s="1"/>
     </row>
     <row r="52" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
-      <c r="B52" s="40"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="3"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="23"/>
+      <c r="J52" s="25"/>
+      <c r="K52" s="23"/>
+      <c r="L52" s="25"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="27"/>
       <c r="O52" s="1"/>
     </row>
     <row r="53" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
-      <c r="B53" s="40"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="3"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="23"/>
+      <c r="H53" s="24"/>
+      <c r="I53" s="23"/>
+      <c r="J53" s="25"/>
+      <c r="K53" s="23"/>
+      <c r="L53" s="25"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="27"/>
       <c r="O53" s="1"/>
     </row>
     <row r="54" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A54" s="1"/>
-      <c r="B54" s="40"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-      <c r="N54" s="3"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="23"/>
+      <c r="L54" s="25"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="27"/>
       <c r="O54" s="1"/>
     </row>
     <row r="55" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A55" s="1"/>
-      <c r="B55" s="40"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
-      <c r="N55" s="3"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="23"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="23"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="23"/>
+      <c r="L55" s="25"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="27"/>
       <c r="O55" s="1"/>
     </row>
     <row r="56" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A56" s="1"/>
-      <c r="B56" s="40"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-      <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
-      <c r="N56" s="3"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="23"/>
+      <c r="L56" s="25"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="27"/>
       <c r="O56" s="1"/>
     </row>
     <row r="57" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
-      <c r="B57" s="40"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="3"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="23"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="23"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="23"/>
+      <c r="L57" s="25"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="27"/>
       <c r="O57" s="1"/>
     </row>
     <row r="58" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A58" s="1"/>
-      <c r="B58" s="40"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="3"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="25"/>
+      <c r="K58" s="23"/>
+      <c r="L58" s="25"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="27"/>
       <c r="O58" s="1"/>
     </row>
     <row r="59" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
-      <c r="B59" s="40"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="3"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="24"/>
+      <c r="I59" s="23"/>
+      <c r="J59" s="25"/>
+      <c r="K59" s="23"/>
+      <c r="L59" s="25"/>
+      <c r="M59" s="26"/>
+      <c r="N59" s="27"/>
       <c r="O59" s="1"/>
     </row>
     <row r="60" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
-      <c r="B60" s="40"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="40"/>
-      <c r="E60" s="40"/>
-      <c r="F60" s="40"/>
-      <c r="G60" s="40"/>
-      <c r="H60" s="40"/>
-      <c r="I60" s="40"/>
-      <c r="J60" s="40"/>
-      <c r="K60" s="40"/>
-      <c r="L60" s="40"/>
-      <c r="M60" s="40"/>
-      <c r="N60" s="3"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="23"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="23"/>
+      <c r="J60" s="25"/>
+      <c r="K60" s="23"/>
+      <c r="L60" s="25"/>
+      <c r="M60" s="26"/>
+      <c r="N60" s="27"/>
       <c r="O60" s="1"/>
     </row>
     <row r="61" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="40"/>
-      <c r="D61" s="40"/>
-      <c r="E61" s="40"/>
-      <c r="F61" s="40"/>
-      <c r="G61" s="40"/>
-      <c r="H61" s="40"/>
-      <c r="I61" s="40"/>
-      <c r="J61" s="40"/>
-      <c r="K61" s="40"/>
-      <c r="L61" s="40"/>
-      <c r="M61" s="40"/>
-      <c r="N61" s="3"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="23"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="23"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="23"/>
+      <c r="L61" s="25"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="27"/>
       <c r="O61" s="1"/>
     </row>
     <row r="62" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
-      <c r="B62" s="44"/>
-      <c r="C62" s="44"/>
-      <c r="D62" s="44"/>
-      <c r="E62" s="44"/>
-      <c r="F62" s="44"/>
-      <c r="G62" s="44"/>
-      <c r="H62" s="44"/>
-      <c r="I62" s="44"/>
-      <c r="J62" s="44"/>
-      <c r="K62" s="44"/>
-      <c r="L62" s="44"/>
-      <c r="M62" s="44"/>
-      <c r="N62" s="44"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="23"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="23"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="23"/>
+      <c r="L62" s="25"/>
+      <c r="M62" s="26"/>
+      <c r="N62" s="27"/>
       <c r="O62" s="1"/>
     </row>
     <row r="63" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
-      <c r="B63" s="44"/>
-      <c r="C63" s="44"/>
-      <c r="D63" s="44"/>
-      <c r="E63" s="44"/>
-      <c r="F63" s="44"/>
-      <c r="G63" s="44"/>
-      <c r="H63" s="44"/>
-      <c r="I63" s="44"/>
-      <c r="J63" s="44"/>
-      <c r="K63" s="44"/>
-      <c r="L63" s="44"/>
-      <c r="M63" s="44"/>
-      <c r="N63" s="3"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="23"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="23"/>
+      <c r="J63" s="25"/>
+      <c r="K63" s="23"/>
+      <c r="L63" s="25"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="27"/>
       <c r="O63" s="1"/>
     </row>
     <row r="64" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A64" s="1"/>
-      <c r="B64" s="40"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
-      <c r="N64" s="3"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="23"/>
+      <c r="J64" s="25"/>
+      <c r="K64" s="23"/>
+      <c r="L64" s="25"/>
+      <c r="M64" s="26"/>
+      <c r="N64" s="27"/>
       <c r="O64" s="1"/>
     </row>
     <row r="65" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
-      <c r="B65" s="40"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="3"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="23"/>
+      <c r="J65" s="25"/>
+      <c r="K65" s="23"/>
+      <c r="L65" s="25"/>
+      <c r="M65" s="26"/>
+      <c r="N65" s="27"/>
       <c r="O65" s="1"/>
     </row>
     <row r="66" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
-      <c r="B66" s="40"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
-      <c r="N66" s="3"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="36"/>
+      <c r="I66" s="35"/>
+      <c r="J66" s="37"/>
+      <c r="K66" s="35"/>
+      <c r="L66" s="37"/>
+      <c r="M66" s="38"/>
+      <c r="N66" s="39"/>
       <c r="O66" s="1"/>
     </row>
     <row r="67" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
@@ -2543,72 +2541,74 @@
       <c r="N67" s="3"/>
       <c r="O67" s="1"/>
     </row>
-    <row r="68" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" ht="19.5" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
-      <c r="B68" s="44"/>
-      <c r="C68" s="44"/>
-      <c r="D68" s="44"/>
-      <c r="E68" s="44"/>
-      <c r="F68" s="44"/>
-      <c r="G68" s="44"/>
-      <c r="H68" s="44"/>
-      <c r="I68" s="44"/>
-      <c r="J68" s="44"/>
-      <c r="K68" s="44"/>
-      <c r="L68" s="44"/>
-      <c r="M68" s="44"/>
-      <c r="N68" s="44"/>
+      <c r="B68" s="40"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="41"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="41"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="N68" s="43"/>
       <c r="O68" s="1"/>
     </row>
     <row r="69" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
-      <c r="B69" s="44"/>
-      <c r="C69" s="44"/>
-      <c r="D69" s="44"/>
-      <c r="E69" s="44"/>
-      <c r="F69" s="44"/>
-      <c r="G69" s="44"/>
-      <c r="H69" s="44"/>
-      <c r="I69" s="44"/>
-      <c r="J69" s="44"/>
-      <c r="K69" s="44"/>
-      <c r="L69" s="44"/>
-      <c r="M69" s="44"/>
-      <c r="N69" s="44"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="3"/>
       <c r="O69" s="1"/>
     </row>
     <row r="70" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
-      <c r="B70" s="44"/>
-      <c r="C70" s="44"/>
-      <c r="D70" s="44"/>
-      <c r="E70" s="44"/>
-      <c r="F70" s="44"/>
-      <c r="G70" s="44"/>
-      <c r="H70" s="44"/>
-      <c r="I70" s="44"/>
-      <c r="J70" s="44"/>
-      <c r="K70" s="44"/>
-      <c r="L70" s="44"/>
-      <c r="M70" s="44"/>
-      <c r="N70" s="44"/>
+      <c r="B70" s="40"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="3"/>
       <c r="O70" s="1"/>
     </row>
     <row r="71" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
-      <c r="B71" s="44"/>
-      <c r="C71" s="44"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="44"/>
-      <c r="F71" s="44"/>
-      <c r="G71" s="44"/>
-      <c r="H71" s="44"/>
-      <c r="I71" s="44"/>
-      <c r="J71" s="44"/>
-      <c r="K71" s="44"/>
-      <c r="L71" s="44"/>
-      <c r="M71" s="44"/>
-      <c r="N71" s="44"/>
+      <c r="B71" s="40"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="3"/>
       <c r="O71" s="1"/>
     </row>
     <row r="72" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
@@ -2784,68 +2784,68 @@
     <row r="82" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A82" s="1"/>
       <c r="B82" s="40"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="40"/>
+      <c r="H82" s="40"/>
+      <c r="I82" s="40"/>
+      <c r="J82" s="40"/>
+      <c r="K82" s="40"/>
+      <c r="L82" s="40"/>
+      <c r="M82" s="40"/>
       <c r="N82" s="3"/>
       <c r="O82" s="1"/>
     </row>
     <row r="83" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A83" s="1"/>
       <c r="B83" s="40"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-      <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="40"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
+      <c r="G83" s="40"/>
+      <c r="H83" s="40"/>
+      <c r="I83" s="40"/>
+      <c r="J83" s="40"/>
+      <c r="K83" s="40"/>
+      <c r="L83" s="40"/>
+      <c r="M83" s="40"/>
       <c r="N83" s="3"/>
       <c r="O83" s="1"/>
     </row>
     <row r="84" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
-      <c r="B84" s="40"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
-      <c r="N84" s="3"/>
+      <c r="B84" s="44"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="44"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="44"/>
+      <c r="I84" s="44"/>
+      <c r="J84" s="44"/>
+      <c r="K84" s="44"/>
+      <c r="L84" s="44"/>
+      <c r="M84" s="44"/>
+      <c r="N84" s="44"/>
       <c r="O84" s="1"/>
     </row>
     <row r="85" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A85" s="1"/>
-      <c r="B85" s="40"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
+      <c r="B85" s="44"/>
+      <c r="C85" s="44"/>
+      <c r="D85" s="44"/>
+      <c r="E85" s="44"/>
+      <c r="F85" s="44"/>
+      <c r="G85" s="44"/>
+      <c r="H85" s="44"/>
+      <c r="I85" s="44"/>
+      <c r="J85" s="44"/>
+      <c r="K85" s="44"/>
+      <c r="L85" s="44"/>
+      <c r="M85" s="44"/>
       <c r="N85" s="3"/>
       <c r="O85" s="1"/>
     </row>
@@ -2919,70 +2919,70 @@
     </row>
     <row r="90" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A90" s="1"/>
-      <c r="B90" s="40"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
-      <c r="N90" s="3"/>
+      <c r="B90" s="44"/>
+      <c r="C90" s="44"/>
+      <c r="D90" s="44"/>
+      <c r="E90" s="44"/>
+      <c r="F90" s="44"/>
+      <c r="G90" s="44"/>
+      <c r="H90" s="44"/>
+      <c r="I90" s="44"/>
+      <c r="J90" s="44"/>
+      <c r="K90" s="44"/>
+      <c r="L90" s="44"/>
+      <c r="M90" s="44"/>
+      <c r="N90" s="44"/>
       <c r="O90" s="1"/>
     </row>
     <row r="91" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A91" s="1"/>
-      <c r="B91" s="40"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
-      <c r="N91" s="3"/>
+      <c r="B91" s="44"/>
+      <c r="C91" s="44"/>
+      <c r="D91" s="44"/>
+      <c r="E91" s="44"/>
+      <c r="F91" s="44"/>
+      <c r="G91" s="44"/>
+      <c r="H91" s="44"/>
+      <c r="I91" s="44"/>
+      <c r="J91" s="44"/>
+      <c r="K91" s="44"/>
+      <c r="L91" s="44"/>
+      <c r="M91" s="44"/>
+      <c r="N91" s="44"/>
       <c r="O91" s="1"/>
     </row>
     <row r="92" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A92" s="1"/>
-      <c r="B92" s="40"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
-      <c r="N92" s="3"/>
+      <c r="B92" s="44"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="44"/>
+      <c r="F92" s="44"/>
+      <c r="G92" s="44"/>
+      <c r="H92" s="44"/>
+      <c r="I92" s="44"/>
+      <c r="J92" s="44"/>
+      <c r="K92" s="44"/>
+      <c r="L92" s="44"/>
+      <c r="M92" s="44"/>
+      <c r="N92" s="44"/>
       <c r="O92" s="1"/>
     </row>
     <row r="93" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A93" s="1"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
-      <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
-      <c r="N93" s="3"/>
+      <c r="B93" s="44"/>
+      <c r="C93" s="44"/>
+      <c r="D93" s="44"/>
+      <c r="E93" s="44"/>
+      <c r="F93" s="44"/>
+      <c r="G93" s="44"/>
+      <c r="H93" s="44"/>
+      <c r="I93" s="44"/>
+      <c r="J93" s="44"/>
+      <c r="K93" s="44"/>
+      <c r="L93" s="44"/>
+      <c r="M93" s="44"/>
+      <c r="N93" s="44"/>
       <c r="O93" s="1"/>
     </row>
     <row r="94" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
@@ -4653,7 +4653,7 @@
     </row>
     <row r="192" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A192" s="1"/>
-      <c r="B192" s="45"/>
+      <c r="B192" s="40"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
@@ -4687,7 +4687,7 @@
     </row>
     <row r="194" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A194" s="1"/>
-      <c r="B194" s="45"/>
+      <c r="B194" s="40"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
@@ -4721,7 +4721,7 @@
     </row>
     <row r="196" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A196" s="1"/>
-      <c r="B196" s="45"/>
+      <c r="B196" s="40"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
@@ -4755,7 +4755,7 @@
     </row>
     <row r="198" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A198" s="1"/>
-      <c r="B198" s="45"/>
+      <c r="B198" s="40"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
@@ -4789,7 +4789,7 @@
     </row>
     <row r="200" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A200" s="1"/>
-      <c r="B200" s="45"/>
+      <c r="B200" s="40"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
@@ -4823,7 +4823,7 @@
     </row>
     <row r="202" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A202" s="1"/>
-      <c r="B202" s="45"/>
+      <c r="B202" s="40"/>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="204" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A204" s="1"/>
-      <c r="B204" s="45"/>
+      <c r="B204" s="40"/>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="206" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A206" s="1"/>
-      <c r="B206" s="45"/>
+      <c r="B206" s="40"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
@@ -4925,7 +4925,7 @@
     </row>
     <row r="208" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A208" s="1"/>
-      <c r="B208" s="45"/>
+      <c r="B208" s="40"/>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="210" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A210" s="1"/>
-      <c r="B210" s="45"/>
+      <c r="B210" s="40"/>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
@@ -4993,7 +4993,7 @@
     </row>
     <row r="212" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A212" s="1"/>
-      <c r="B212" s="45"/>
+      <c r="B212" s="40"/>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
@@ -11315,79 +11315,387 @@
       <c r="N583" s="3"/>
       <c r="O583" s="1"/>
     </row>
-    <row r="584" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B584" s="46"/>
-    </row>
-    <row r="585" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B585" s="49"/>
-    </row>
-    <row r="586" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B586" s="46"/>
-    </row>
-    <row r="587" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B587" s="49"/>
-    </row>
-    <row r="588" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B588" s="46"/>
-    </row>
-    <row r="589" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B589" s="49"/>
-    </row>
-    <row r="590" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B590" s="46"/>
-    </row>
-    <row r="591" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B591" s="49"/>
-    </row>
-    <row r="592" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B592" s="46"/>
-    </row>
-    <row r="593" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B593" s="49"/>
-    </row>
-    <row r="594" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B594" s="46"/>
-    </row>
-    <row r="595" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B595" s="49"/>
-    </row>
-    <row r="596" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B596" s="46"/>
-    </row>
-    <row r="597" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B597" s="49"/>
-    </row>
-    <row r="598" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B598" s="46"/>
-    </row>
-    <row r="599" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B599" s="49"/>
-    </row>
-    <row r="600" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B600" s="46"/>
-    </row>
-    <row r="601" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B601" s="49"/>
-    </row>
-    <row r="602" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B602" s="46"/>
-    </row>
-    <row r="603" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B603" s="49"/>
-    </row>
-    <row r="604" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B604" s="46"/>
-    </row>
-    <row r="605" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B605" s="49"/>
-    </row>
-    <row r="606" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A584" s="1"/>
+      <c r="B584" s="45"/>
+      <c r="C584" s="2"/>
+      <c r="D584" s="2"/>
+      <c r="E584" s="2"/>
+      <c r="F584" s="2"/>
+      <c r="G584" s="2"/>
+      <c r="H584" s="2"/>
+      <c r="I584" s="2"/>
+      <c r="J584" s="2"/>
+      <c r="K584" s="2"/>
+      <c r="L584" s="2"/>
+      <c r="M584" s="2"/>
+      <c r="N584" s="3"/>
+      <c r="O584" s="1"/>
+    </row>
+    <row r="585" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A585" s="1"/>
+      <c r="B585" s="40"/>
+      <c r="C585" s="2"/>
+      <c r="D585" s="2"/>
+      <c r="E585" s="2"/>
+      <c r="F585" s="2"/>
+      <c r="G585" s="2"/>
+      <c r="H585" s="2"/>
+      <c r="I585" s="2"/>
+      <c r="J585" s="2"/>
+      <c r="K585" s="2"/>
+      <c r="L585" s="2"/>
+      <c r="M585" s="2"/>
+      <c r="N585" s="3"/>
+      <c r="O585" s="1"/>
+    </row>
+    <row r="586" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A586" s="1"/>
+      <c r="B586" s="45"/>
+      <c r="C586" s="2"/>
+      <c r="D586" s="2"/>
+      <c r="E586" s="2"/>
+      <c r="F586" s="2"/>
+      <c r="G586" s="2"/>
+      <c r="H586" s="2"/>
+      <c r="I586" s="2"/>
+      <c r="J586" s="2"/>
+      <c r="K586" s="2"/>
+      <c r="L586" s="2"/>
+      <c r="M586" s="2"/>
+      <c r="N586" s="3"/>
+      <c r="O586" s="1"/>
+    </row>
+    <row r="587" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A587" s="1"/>
+      <c r="B587" s="40"/>
+      <c r="C587" s="2"/>
+      <c r="D587" s="2"/>
+      <c r="E587" s="2"/>
+      <c r="F587" s="2"/>
+      <c r="G587" s="2"/>
+      <c r="H587" s="2"/>
+      <c r="I587" s="2"/>
+      <c r="J587" s="2"/>
+      <c r="K587" s="2"/>
+      <c r="L587" s="2"/>
+      <c r="M587" s="2"/>
+      <c r="N587" s="3"/>
+      <c r="O587" s="1"/>
+    </row>
+    <row r="588" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A588" s="1"/>
+      <c r="B588" s="45"/>
+      <c r="C588" s="2"/>
+      <c r="D588" s="2"/>
+      <c r="E588" s="2"/>
+      <c r="F588" s="2"/>
+      <c r="G588" s="2"/>
+      <c r="H588" s="2"/>
+      <c r="I588" s="2"/>
+      <c r="J588" s="2"/>
+      <c r="K588" s="2"/>
+      <c r="L588" s="2"/>
+      <c r="M588" s="2"/>
+      <c r="N588" s="3"/>
+      <c r="O588" s="1"/>
+    </row>
+    <row r="589" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A589" s="1"/>
+      <c r="B589" s="40"/>
+      <c r="C589" s="2"/>
+      <c r="D589" s="2"/>
+      <c r="E589" s="2"/>
+      <c r="F589" s="2"/>
+      <c r="G589" s="2"/>
+      <c r="H589" s="2"/>
+      <c r="I589" s="2"/>
+      <c r="J589" s="2"/>
+      <c r="K589" s="2"/>
+      <c r="L589" s="2"/>
+      <c r="M589" s="2"/>
+      <c r="N589" s="3"/>
+      <c r="O589" s="1"/>
+    </row>
+    <row r="590" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A590" s="1"/>
+      <c r="B590" s="45"/>
+      <c r="C590" s="2"/>
+      <c r="D590" s="2"/>
+      <c r="E590" s="2"/>
+      <c r="F590" s="2"/>
+      <c r="G590" s="2"/>
+      <c r="H590" s="2"/>
+      <c r="I590" s="2"/>
+      <c r="J590" s="2"/>
+      <c r="K590" s="2"/>
+      <c r="L590" s="2"/>
+      <c r="M590" s="2"/>
+      <c r="N590" s="3"/>
+      <c r="O590" s="1"/>
+    </row>
+    <row r="591" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A591" s="1"/>
+      <c r="B591" s="40"/>
+      <c r="C591" s="2"/>
+      <c r="D591" s="2"/>
+      <c r="E591" s="2"/>
+      <c r="F591" s="2"/>
+      <c r="G591" s="2"/>
+      <c r="H591" s="2"/>
+      <c r="I591" s="2"/>
+      <c r="J591" s="2"/>
+      <c r="K591" s="2"/>
+      <c r="L591" s="2"/>
+      <c r="M591" s="2"/>
+      <c r="N591" s="3"/>
+      <c r="O591" s="1"/>
+    </row>
+    <row r="592" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A592" s="1"/>
+      <c r="B592" s="45"/>
+      <c r="C592" s="2"/>
+      <c r="D592" s="2"/>
+      <c r="E592" s="2"/>
+      <c r="F592" s="2"/>
+      <c r="G592" s="2"/>
+      <c r="H592" s="2"/>
+      <c r="I592" s="2"/>
+      <c r="J592" s="2"/>
+      <c r="K592" s="2"/>
+      <c r="L592" s="2"/>
+      <c r="M592" s="2"/>
+      <c r="N592" s="3"/>
+      <c r="O592" s="1"/>
+    </row>
+    <row r="593" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A593" s="1"/>
+      <c r="B593" s="40"/>
+      <c r="C593" s="2"/>
+      <c r="D593" s="2"/>
+      <c r="E593" s="2"/>
+      <c r="F593" s="2"/>
+      <c r="G593" s="2"/>
+      <c r="H593" s="2"/>
+      <c r="I593" s="2"/>
+      <c r="J593" s="2"/>
+      <c r="K593" s="2"/>
+      <c r="L593" s="2"/>
+      <c r="M593" s="2"/>
+      <c r="N593" s="3"/>
+      <c r="O593" s="1"/>
+    </row>
+    <row r="594" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A594" s="1"/>
+      <c r="B594" s="45"/>
+      <c r="C594" s="2"/>
+      <c r="D594" s="2"/>
+      <c r="E594" s="2"/>
+      <c r="F594" s="2"/>
+      <c r="G594" s="2"/>
+      <c r="H594" s="2"/>
+      <c r="I594" s="2"/>
+      <c r="J594" s="2"/>
+      <c r="K594" s="2"/>
+      <c r="L594" s="2"/>
+      <c r="M594" s="2"/>
+      <c r="N594" s="3"/>
+      <c r="O594" s="1"/>
+    </row>
+    <row r="595" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A595" s="1"/>
+      <c r="B595" s="40"/>
+      <c r="C595" s="2"/>
+      <c r="D595" s="2"/>
+      <c r="E595" s="2"/>
+      <c r="F595" s="2"/>
+      <c r="G595" s="2"/>
+      <c r="H595" s="2"/>
+      <c r="I595" s="2"/>
+      <c r="J595" s="2"/>
+      <c r="K595" s="2"/>
+      <c r="L595" s="2"/>
+      <c r="M595" s="2"/>
+      <c r="N595" s="3"/>
+      <c r="O595" s="1"/>
+    </row>
+    <row r="596" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A596" s="1"/>
+      <c r="B596" s="45"/>
+      <c r="C596" s="2"/>
+      <c r="D596" s="2"/>
+      <c r="E596" s="2"/>
+      <c r="F596" s="2"/>
+      <c r="G596" s="2"/>
+      <c r="H596" s="2"/>
+      <c r="I596" s="2"/>
+      <c r="J596" s="2"/>
+      <c r="K596" s="2"/>
+      <c r="L596" s="2"/>
+      <c r="M596" s="2"/>
+      <c r="N596" s="3"/>
+      <c r="O596" s="1"/>
+    </row>
+    <row r="597" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A597" s="1"/>
+      <c r="B597" s="40"/>
+      <c r="C597" s="2"/>
+      <c r="D597" s="2"/>
+      <c r="E597" s="2"/>
+      <c r="F597" s="2"/>
+      <c r="G597" s="2"/>
+      <c r="H597" s="2"/>
+      <c r="I597" s="2"/>
+      <c r="J597" s="2"/>
+      <c r="K597" s="2"/>
+      <c r="L597" s="2"/>
+      <c r="M597" s="2"/>
+      <c r="N597" s="3"/>
+      <c r="O597" s="1"/>
+    </row>
+    <row r="598" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A598" s="1"/>
+      <c r="B598" s="45"/>
+      <c r="C598" s="2"/>
+      <c r="D598" s="2"/>
+      <c r="E598" s="2"/>
+      <c r="F598" s="2"/>
+      <c r="G598" s="2"/>
+      <c r="H598" s="2"/>
+      <c r="I598" s="2"/>
+      <c r="J598" s="2"/>
+      <c r="K598" s="2"/>
+      <c r="L598" s="2"/>
+      <c r="M598" s="2"/>
+      <c r="N598" s="3"/>
+      <c r="O598" s="1"/>
+    </row>
+    <row r="599" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A599" s="1"/>
+      <c r="B599" s="40"/>
+      <c r="C599" s="2"/>
+      <c r="D599" s="2"/>
+      <c r="E599" s="2"/>
+      <c r="F599" s="2"/>
+      <c r="G599" s="2"/>
+      <c r="H599" s="2"/>
+      <c r="I599" s="2"/>
+      <c r="J599" s="2"/>
+      <c r="K599" s="2"/>
+      <c r="L599" s="2"/>
+      <c r="M599" s="2"/>
+      <c r="N599" s="3"/>
+      <c r="O599" s="1"/>
+    </row>
+    <row r="600" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A600" s="1"/>
+      <c r="B600" s="45"/>
+      <c r="C600" s="2"/>
+      <c r="D600" s="2"/>
+      <c r="E600" s="2"/>
+      <c r="F600" s="2"/>
+      <c r="G600" s="2"/>
+      <c r="H600" s="2"/>
+      <c r="I600" s="2"/>
+      <c r="J600" s="2"/>
+      <c r="K600" s="2"/>
+      <c r="L600" s="2"/>
+      <c r="M600" s="2"/>
+      <c r="N600" s="3"/>
+      <c r="O600" s="1"/>
+    </row>
+    <row r="601" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A601" s="1"/>
+      <c r="B601" s="40"/>
+      <c r="C601" s="2"/>
+      <c r="D601" s="2"/>
+      <c r="E601" s="2"/>
+      <c r="F601" s="2"/>
+      <c r="G601" s="2"/>
+      <c r="H601" s="2"/>
+      <c r="I601" s="2"/>
+      <c r="J601" s="2"/>
+      <c r="K601" s="2"/>
+      <c r="L601" s="2"/>
+      <c r="M601" s="2"/>
+      <c r="N601" s="3"/>
+      <c r="O601" s="1"/>
+    </row>
+    <row r="602" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A602" s="1"/>
+      <c r="B602" s="45"/>
+      <c r="C602" s="2"/>
+      <c r="D602" s="2"/>
+      <c r="E602" s="2"/>
+      <c r="F602" s="2"/>
+      <c r="G602" s="2"/>
+      <c r="H602" s="2"/>
+      <c r="I602" s="2"/>
+      <c r="J602" s="2"/>
+      <c r="K602" s="2"/>
+      <c r="L602" s="2"/>
+      <c r="M602" s="2"/>
+      <c r="N602" s="3"/>
+      <c r="O602" s="1"/>
+    </row>
+    <row r="603" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A603" s="1"/>
+      <c r="B603" s="40"/>
+      <c r="C603" s="2"/>
+      <c r="D603" s="2"/>
+      <c r="E603" s="2"/>
+      <c r="F603" s="2"/>
+      <c r="G603" s="2"/>
+      <c r="H603" s="2"/>
+      <c r="I603" s="2"/>
+      <c r="J603" s="2"/>
+      <c r="K603" s="2"/>
+      <c r="L603" s="2"/>
+      <c r="M603" s="2"/>
+      <c r="N603" s="3"/>
+      <c r="O603" s="1"/>
+    </row>
+    <row r="604" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A604" s="1"/>
+      <c r="B604" s="45"/>
+      <c r="C604" s="2"/>
+      <c r="D604" s="2"/>
+      <c r="E604" s="2"/>
+      <c r="F604" s="2"/>
+      <c r="G604" s="2"/>
+      <c r="H604" s="2"/>
+      <c r="I604" s="2"/>
+      <c r="J604" s="2"/>
+      <c r="K604" s="2"/>
+      <c r="L604" s="2"/>
+      <c r="M604" s="2"/>
+      <c r="N604" s="3"/>
+      <c r="O604" s="1"/>
+    </row>
+    <row r="605" spans="1:15" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A605" s="1"/>
+      <c r="B605" s="40"/>
+      <c r="C605" s="2"/>
+      <c r="D605" s="2"/>
+      <c r="E605" s="2"/>
+      <c r="F605" s="2"/>
+      <c r="G605" s="2"/>
+      <c r="H605" s="2"/>
+      <c r="I605" s="2"/>
+      <c r="J605" s="2"/>
+      <c r="K605" s="2"/>
+      <c r="L605" s="2"/>
+      <c r="M605" s="2"/>
+      <c r="N605" s="3"/>
+      <c r="O605" s="1"/>
+    </row>
+    <row r="606" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B606" s="46"/>
     </row>
-    <row r="607" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B607" s="49"/>
     </row>
-    <row r="608" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B608" s="46"/>
     </row>
     <row r="609" spans="2:2" x14ac:dyDescent="0.25">
@@ -12393,67 +12701,67 @@
       <c r="B942" s="46"/>
     </row>
     <row r="943" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B943" s="46"/>
+      <c r="B943" s="49"/>
     </row>
     <row r="944" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B944" s="46"/>
     </row>
     <row r="945" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B945" s="46"/>
+      <c r="B945" s="49"/>
     </row>
     <row r="946" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B946" s="46"/>
     </row>
     <row r="947" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B947" s="46"/>
+      <c r="B947" s="49"/>
     </row>
     <row r="948" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B948" s="46"/>
     </row>
     <row r="949" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B949" s="46"/>
+      <c r="B949" s="49"/>
     </row>
     <row r="950" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B950" s="46"/>
     </row>
     <row r="951" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B951" s="46"/>
+      <c r="B951" s="49"/>
     </row>
     <row r="952" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B952" s="46"/>
     </row>
     <row r="953" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B953" s="46"/>
+      <c r="B953" s="49"/>
     </row>
     <row r="954" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B954" s="46"/>
     </row>
     <row r="955" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B955" s="46"/>
+      <c r="B955" s="49"/>
     </row>
     <row r="956" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B956" s="46"/>
     </row>
     <row r="957" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B957" s="46"/>
+      <c r="B957" s="49"/>
     </row>
     <row r="958" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B958" s="46"/>
     </row>
     <row r="959" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B959" s="46"/>
+      <c r="B959" s="49"/>
     </row>
     <row r="960" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B960" s="46"/>
     </row>
     <row r="961" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B961" s="46"/>
+      <c r="B961" s="49"/>
     </row>
     <row r="962" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B962" s="46"/>
     </row>
     <row r="963" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B963" s="46"/>
+      <c r="B963" s="49"/>
     </row>
     <row r="964" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B964" s="46"/>
@@ -14008,6 +14316,72 @@
     </row>
     <row r="1481" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1481" s="46"/>
+    </row>
+    <row r="1482" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1482" s="46"/>
+    </row>
+    <row r="1483" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1483" s="46"/>
+    </row>
+    <row r="1484" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1484" s="46"/>
+    </row>
+    <row r="1485" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1485" s="46"/>
+    </row>
+    <row r="1486" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1486" s="46"/>
+    </row>
+    <row r="1487" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1487" s="46"/>
+    </row>
+    <row r="1488" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1488" s="46"/>
+    </row>
+    <row r="1489" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1489" s="46"/>
+    </row>
+    <row r="1490" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1490" s="46"/>
+    </row>
+    <row r="1491" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1491" s="46"/>
+    </row>
+    <row r="1492" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1492" s="46"/>
+    </row>
+    <row r="1493" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1493" s="46"/>
+    </row>
+    <row r="1494" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1494" s="46"/>
+    </row>
+    <row r="1495" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1495" s="46"/>
+    </row>
+    <row r="1496" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1496" s="46"/>
+    </row>
+    <row r="1497" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1497" s="46"/>
+    </row>
+    <row r="1498" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1498" s="46"/>
+    </row>
+    <row r="1499" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1499" s="46"/>
+    </row>
+    <row r="1500" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1500" s="46"/>
+    </row>
+    <row r="1501" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1501" s="46"/>
+    </row>
+    <row r="1502" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1502" s="46"/>
+    </row>
+    <row r="1503" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1503" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="10">
